--- a/data/trans_dic/P20B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P20B-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que estuvo en lista de espera por ingreso hospitalario</t>
+          <t>Población que estuvo en lista de espera por ingreso hospitalario (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,27; 55,59</t>
+          <t>8,37; 55,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,55; 71,94</t>
+          <t>28,85; 71,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,01; 61,55</t>
+          <t>13,33; 61,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,12</t>
+          <t>0,0; 49,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,28; 44,39</t>
+          <t>15,36; 45,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,58; 32,05</t>
+          <t>7,73; 34,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 27,31</t>
+          <t>5,62; 29,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 29,7</t>
+          <t>3,57; 30,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,79; 51,86</t>
+          <t>25,08; 50,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,5; 36,85</t>
+          <t>12,65; 36,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 31,88</t>
+          <t>6,83; 31,0</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 37,05</t>
+          <t>7,25; 40,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,85; 45,31</t>
+          <t>12,53; 44,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,93; 53,93</t>
+          <t>11,47; 54,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,25; 57,03</t>
+          <t>22,39; 56,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,07; 33,38</t>
+          <t>8,7; 30,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,41; 38,02</t>
+          <t>14,18; 38,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,36; 43,21</t>
+          <t>10,28; 41,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,28; 47,36</t>
+          <t>14,11; 46,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,07; 29,32</t>
+          <t>11,22; 29,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,96; 36,11</t>
+          <t>17,23; 35,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,22; 43,71</t>
+          <t>15,11; 40,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,89; 48,36</t>
+          <t>21,61; 47,66</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,43</t>
+          <t>0,0; 53,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,11; 40,16</t>
+          <t>8,33; 42,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,6; 59,76</t>
+          <t>8,45; 59,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,02; 56,43</t>
+          <t>25,68; 59,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,49</t>
+          <t>0,0; 37,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,44; 45,83</t>
+          <t>14,58; 45,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 39,03</t>
+          <t>9,87; 39,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,15; 34,61</t>
+          <t>11,49; 33,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 31,18</t>
+          <t>3,74; 32,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,01; 36,76</t>
+          <t>13,73; 35,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,38; 37,29</t>
+          <t>12,02; 38,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,23; 41,37</t>
+          <t>20,47; 40,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,87</t>
+          <t>0,0; 53,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,03; 47,42</t>
+          <t>8,97; 47,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,81; 49,68</t>
+          <t>14,09; 49,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,16; 60,55</t>
+          <t>16,44; 58,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,55; 56,87</t>
+          <t>18,56; 63,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 36,8</t>
+          <t>8,82; 38,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,82; 56,88</t>
+          <t>17,41; 55,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,0; 52,49</t>
+          <t>15,43; 56,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,0; 47,55</t>
+          <t>13,71; 49,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,61; 35,81</t>
+          <t>11,9; 33,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,38; 47,93</t>
+          <t>20,47; 46,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,53; 48,39</t>
+          <t>20,18; 49,11</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 47,58</t>
+          <t>5,98; 48,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,53; 78,6</t>
+          <t>22,63; 78,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,01; 88,49</t>
+          <t>21,96; 87,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 88,5</t>
+          <t>15,19; 88,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,88</t>
+          <t>0,0; 22,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,8; 56,03</t>
+          <t>9,74; 51,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,06; 67,93</t>
+          <t>8,57; 66,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 34,06</t>
+          <t>4,06; 33,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 25,84</t>
+          <t>2,84; 27,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,71; 54,5</t>
+          <t>22,91; 53,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,46; 66,24</t>
+          <t>22,29; 66,3</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,21; 46,23</t>
+          <t>12,74; 48,21</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,58; 71,26</t>
+          <t>8,3; 62,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,34; 62,97</t>
+          <t>7,38; 64,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,15; 62,69</t>
+          <t>14,61; 59,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,7; 40,89</t>
+          <t>15,07; 40,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,52; 37,28</t>
+          <t>6,95; 36,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,86; 32,25</t>
+          <t>3,88; 35,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,87; 51,56</t>
+          <t>14,82; 52,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,6; 31,1</t>
+          <t>4,83; 29,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,27; 39,13</t>
+          <t>11,9; 38,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,39; 41,8</t>
+          <t>10,15; 40,22</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20,33; 49,34</t>
+          <t>18,47; 48,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,75; 30,51</t>
+          <t>12,74; 29,86</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,39; 54,75</t>
+          <t>21,87; 54,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,1; 52,97</t>
+          <t>15,36; 50,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,24; 58,84</t>
+          <t>16,11; 58,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,04; 42,44</t>
+          <t>14,32; 42,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,39; 43,77</t>
+          <t>19,4; 43,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,68; 37,92</t>
+          <t>15,85; 39,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,1; 39,2</t>
+          <t>14,09; 39,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,01; 40,57</t>
+          <t>21,09; 40,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23,27; 42,97</t>
+          <t>23,83; 43,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,71; 38,42</t>
+          <t>19,47; 37,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,75; 40,32</t>
+          <t>18,2; 39,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,47; 37,36</t>
+          <t>20,41; 36,77</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,4; 45,16</t>
+          <t>10,77; 44,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,01; 31,9</t>
+          <t>5,44; 31,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,85; 50,03</t>
+          <t>18,12; 50,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,11; 50,17</t>
+          <t>16,79; 50,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,47; 31,91</t>
+          <t>9,6; 32,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,7; 39,09</t>
+          <t>14,98; 38,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,93; 32,48</t>
+          <t>9,18; 32,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,42; 27,69</t>
+          <t>6,23; 28,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,12; 31,01</t>
+          <t>14,14; 31,81</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,99; 32,33</t>
+          <t>13,99; 31,97</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,94; 34,78</t>
+          <t>15,52; 36,33</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,99; 34,01</t>
+          <t>15,29; 36,53</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,86; 34,1</t>
+          <t>19,5; 34,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23,14; 37,79</t>
+          <t>23,73; 37,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26,16; 40,84</t>
+          <t>25,74; 41,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26,4; 39,67</t>
+          <t>26,82; 39,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,68; 25,34</t>
+          <t>14,8; 25,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,77; 29,43</t>
+          <t>19,95; 29,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,18; 29,62</t>
+          <t>18,85; 30,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,29; 27,91</t>
+          <t>18,49; 28,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18,3; 26,69</t>
+          <t>18,71; 26,79</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23,13; 30,62</t>
+          <t>22,6; 30,88</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23,44; 32,62</t>
+          <t>23,71; 32,97</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,49; 31,91</t>
+          <t>23,75; 32,09</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que estuvo en lista de espera por ingreso hospitalario</t>
+          <t>Población que estuvo en lista de espera por ingreso hospitalario (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>834; 5602</t>
+          <t>844; 5587</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7486; 17629</t>
+          <t>7069; 17626</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2036; 9627</t>
+          <t>2084; 9617</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5917</t>
+          <t>0; 5997</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1974</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5275; 16394</t>
+          <t>5671; 16901</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2548; 10774</t>
+          <t>2598; 11500</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1066; 5161</t>
+          <t>1063; 5600</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>813; 6731</t>
+          <t>810; 6933</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15843; 31864</t>
+          <t>15408; 31260</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6158; 18149</t>
+          <t>6229; 17937</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2299; 9862</t>
+          <t>2112; 9592</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1872; 9564</t>
+          <t>1872; 10427</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6271; 19129</t>
+          <t>5290; 18950</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3133; 11321</t>
+          <t>2408; 11511</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8619; 22097</t>
+          <t>8673; 21724</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4761; 15780</t>
+          <t>4114; 14531</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8580; 22642</t>
+          <t>8447; 22693</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3735; 15586</t>
+          <t>3706; 15104</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2977; 10615</t>
+          <t>3162; 10502</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8090; 21432</t>
+          <t>8201; 21522</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17258; 36753</t>
+          <t>17533; 36505</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9257; 24941</t>
+          <t>8620; 23010</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14611; 29577</t>
+          <t>13215; 29148</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4825</t>
+          <t>0; 3917</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1983; 9816</t>
+          <t>2037; 10497</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>780; 5419</t>
+          <t>766; 5401</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6520; 15317</t>
+          <t>6971; 16126</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5956</t>
+          <t>0; 6151</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4903; 15568</t>
+          <t>4953; 15549</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3025; 12676</t>
+          <t>3204; 12871</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3989; 11366</t>
+          <t>3773; 11101</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>890; 7390</t>
+          <t>887; 7748</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8181; 21472</t>
+          <t>8019; 20637</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4729; 15492</t>
+          <t>4992; 16057</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12732; 24813</t>
+          <t>12278; 24363</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4132</t>
+          <t>0; 3957</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1820; 9556</t>
+          <t>1808; 9506</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4156; 13939</t>
+          <t>3954; 13799</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3988; 14070</t>
+          <t>3820; 13587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2707; 10583</t>
+          <t>3454; 11798</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3288; 13427</t>
+          <t>3219; 14062</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6002; 18138</t>
+          <t>5551; 17809</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5045; 17656</t>
+          <t>5191; 19015</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3640; 12364</t>
+          <t>3565; 12761</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7142; 20282</t>
+          <t>6742; 19164</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12816; 28731</t>
+          <t>12269; 27720</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11676; 27522</t>
+          <t>11479; 27929</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>822; 6210</t>
+          <t>781; 6327</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3241; 10388</t>
+          <t>2991; 10339</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1907; 7669</t>
+          <t>1903; 7611</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>623; 3813</t>
+          <t>654; 3806</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5441</t>
+          <t>0; 4290</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2097; 11984</t>
+          <t>2084; 10956</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>906; 7636</t>
+          <t>963; 7487</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>344; 2812</t>
+          <t>335; 2782</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>957; 8242</t>
+          <t>905; 8615</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7168; 18861</t>
+          <t>7928; 18578</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4272; 13187</t>
+          <t>4437; 13199</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1409; 5809</t>
+          <t>1600; 6057</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>898; 7458</t>
+          <t>869; 6550</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1129; 9687</t>
+          <t>1135; 9995</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2755; 11398</t>
+          <t>2657; 10813</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3565; 9916</t>
+          <t>3654; 9774</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2606; 11396</t>
+          <t>2126; 11125</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1033; 8629</t>
+          <t>1037; 9605</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3414; 13673</t>
+          <t>3931; 13878</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1209; 6710</t>
+          <t>1042; 6459</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5448; 16056</t>
+          <t>4882; 15875</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4378; 17614</t>
+          <t>4277; 16950</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9087; 22058</t>
+          <t>8259; 21812</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5846; 13981</t>
+          <t>5838; 13683</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7293; 18662</t>
+          <t>7456; 18525</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4644; 16289</t>
+          <t>4724; 15620</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4248; 15393</t>
+          <t>4215; 15430</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4595; 14958</t>
+          <t>5046; 14900</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9868; 23492</t>
+          <t>10413; 23087</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8614; 22249</t>
+          <t>9299; 23093</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6311; 18890</t>
+          <t>6790; 19176</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>10172; 20626</t>
+          <t>10719; 20605</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20416; 37705</t>
+          <t>20912; 37909</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16729; 34355</t>
+          <t>17410; 33666</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13194; 29979</t>
+          <t>13535; 29514</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>17618; 32159</t>
+          <t>17571; 31651</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2931; 11610</t>
+          <t>2769; 11560</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2230; 11836</t>
+          <t>2018; 11731</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6730; 17865</t>
+          <t>6472; 18035</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3720; 11584</t>
+          <t>3876; 11707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4780; 16112</t>
+          <t>4847; 16227</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8934; 23755</t>
+          <t>9102; 23642</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4423; 16089</t>
+          <t>4545; 15996</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1822; 7861</t>
+          <t>1768; 8050</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9997; 23632</t>
+          <t>10776; 24244</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14671; 31643</t>
+          <t>13694; 31286</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13590; 29645</t>
+          <t>13231; 30969</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7200; 17506</t>
+          <t>7871; 18804</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>25274; 45688</t>
+          <t>26122; 45854</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>48081; 78523</t>
+          <t>49306; 78396</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42502; 66360</t>
+          <t>41819; 67203</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>49639; 74594</t>
+          <t>50441; 74818</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>38941; 62932</t>
+          <t>36755; 62079</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>66124; 98443</t>
+          <t>66734; 98841</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51703; 79847</t>
+          <t>50800; 81415</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>39667; 60527</t>
+          <t>40092; 61718</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>69951; 102057</t>
+          <t>71546; 102438</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>125411; 166042</t>
+          <t>122540; 167472</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>101246; 140920</t>
+          <t>102423; 142450</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>95101; 129204</t>
+          <t>96172; 129947</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P20B-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,37; 55,44</t>
+          <t>8,27; 62,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,85; 71,93</t>
+          <t>30,81; 72,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,33; 61,49</t>
+          <t>12,7; 60,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,79</t>
+          <t>0,0; 49,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,36; 45,76</t>
+          <t>16,3; 46,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 34,21</t>
+          <t>5,66; 31,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 29,64</t>
+          <t>4,89; 26,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 30,59</t>
+          <t>3,57; 30,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,08; 50,88</t>
+          <t>24,98; 49,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,65; 36,42</t>
+          <t>12,35; 36,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 31,0</t>
+          <t>7,27; 29,23</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 40,39</t>
+          <t>7,17; 38,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,53; 44,89</t>
+          <t>13,75; 44,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 54,84</t>
+          <t>11,27; 56,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,39; 56,07</t>
+          <t>26,39; 59,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,7; 30,74</t>
+          <t>10,21; 31,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,18; 38,1</t>
+          <t>14,34; 37,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,28; 41,88</t>
+          <t>11,04; 44,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,11; 46,86</t>
+          <t>14,08; 44,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,22; 29,45</t>
+          <t>11,56; 30,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,23; 35,87</t>
+          <t>17,32; 34,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,11; 40,33</t>
+          <t>17,09; 41,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,61; 47,66</t>
+          <t>23,16; 48,18</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,12</t>
+          <t>0,0; 58,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 42,94</t>
+          <t>7,74; 42,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 59,57</t>
+          <t>8,61; 60,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,68; 59,41</t>
+          <t>24,22; 56,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,68</t>
+          <t>0,0; 40,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,58; 45,78</t>
+          <t>14,68; 45,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,87; 39,63</t>
+          <t>9,78; 38,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,49; 33,8</t>
+          <t>11,62; 33,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 32,69</t>
+          <t>3,78; 29,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,73; 35,33</t>
+          <t>15,16; 37,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,02; 38,65</t>
+          <t>12,03; 37,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,47; 40,61</t>
+          <t>20,7; 39,02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,52</t>
+          <t>0,0; 52,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 47,17</t>
+          <t>8,99; 44,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,09; 49,18</t>
+          <t>14,31; 50,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,44; 58,47</t>
+          <t>20,07; 63,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,56; 63,4</t>
+          <t>15,47; 57,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,82; 38,54</t>
+          <t>9,1; 37,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,41; 55,84</t>
+          <t>17,95; 55,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,43; 56,53</t>
+          <t>15,93; 53,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,71; 49,08</t>
+          <t>13,88; 47,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,9; 33,83</t>
+          <t>11,59; 33,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,47; 46,24</t>
+          <t>19,39; 45,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,18; 49,11</t>
+          <t>21,07; 49,97</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 48,47</t>
+          <t>0,0; 47,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,63; 78,23</t>
+          <t>29,07; 82,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,96; 87,82</t>
+          <t>20,53; 88,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,19; 88,34</t>
+          <t>14,98; 88,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,77</t>
+          <t>0,0; 22,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,74; 51,22</t>
+          <t>9,72; 54,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,57; 66,6</t>
+          <t>8,22; 66,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 33,69</t>
+          <t>4,19; 33,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 27,01</t>
+          <t>2,93; 29,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,91; 53,69</t>
+          <t>22,64; 56,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,29; 66,3</t>
+          <t>23,33; 65,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,74; 48,21</t>
+          <t>12,05; 47,23</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,3; 62,58</t>
+          <t>8,88; 70,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 64,97</t>
+          <t>8,99; 62,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,61; 59,47</t>
+          <t>14,37; 59,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,07; 40,3</t>
+          <t>12,85; 40,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,95; 36,39</t>
+          <t>8,75; 36,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 35,9</t>
+          <t>4,01; 34,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,82; 52,33</t>
+          <t>13,55; 53,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,83; 29,94</t>
+          <t>5,49; 30,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,9; 38,68</t>
+          <t>12,09; 37,92</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,15; 40,22</t>
+          <t>10,05; 38,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,47; 48,79</t>
+          <t>19,89; 48,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,74; 29,86</t>
+          <t>12,23; 30,92</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,87; 54,34</t>
+          <t>20,2; 53,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,36; 50,8</t>
+          <t>16,5; 52,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,11; 58,98</t>
+          <t>13,71; 56,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,32; 42,28</t>
+          <t>12,96; 40,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,4; 43,02</t>
+          <t>18,66; 42,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,85; 39,36</t>
+          <t>14,51; 40,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,09; 39,79</t>
+          <t>13,31; 40,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,09; 40,53</t>
+          <t>21,57; 42,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23,83; 43,2</t>
+          <t>23,85; 44,38</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,47; 37,65</t>
+          <t>18,36; 38,06</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,2; 39,7</t>
+          <t>17,66; 39,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,41; 36,77</t>
+          <t>21,06; 37,39</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,77; 44,96</t>
+          <t>12,12; 45,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,44; 31,62</t>
+          <t>6,24; 32,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,12; 50,5</t>
+          <t>17,34; 49,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,79; 50,7</t>
+          <t>18,76; 51,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,6; 32,14</t>
+          <t>9,47; 30,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,98; 38,9</t>
+          <t>14,84; 40,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,18; 32,29</t>
+          <t>9,12; 32,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,23; 28,36</t>
+          <t>6,11; 27,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,14; 31,81</t>
+          <t>13,04; 30,86</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,99; 31,97</t>
+          <t>14,43; 31,72</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,52; 36,33</t>
+          <t>15,98; 34,68</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,29; 36,53</t>
+          <t>15,08; 34,14</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19,5; 34,22</t>
+          <t>19,75; 33,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23,73; 37,73</t>
+          <t>23,42; 37,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25,74; 41,36</t>
+          <t>26,65; 42,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26,82; 39,78</t>
+          <t>26,74; 39,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,8; 25,0</t>
+          <t>15,55; 25,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,95; 29,55</t>
+          <t>20,11; 29,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,85; 30,21</t>
+          <t>19,59; 30,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,49; 28,46</t>
+          <t>18,47; 29,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18,71; 26,79</t>
+          <t>18,4; 26,81</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22,6; 30,88</t>
+          <t>23,22; 30,67</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23,71; 32,97</t>
+          <t>23,57; 32,47</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,75; 32,09</t>
+          <t>24,16; 32,08</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5134</t>
         </is>
       </c>
     </row>
@@ -2209,22 +2209,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>844; 5587</t>
+          <t>833; 6348</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7069; 17626</t>
+          <t>7549; 17703</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2084; 9617</t>
+          <t>1987; 9461</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5997</t>
+          <t>0; 5768</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5671; 16901</t>
+          <t>6019; 17252</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2598; 11500</t>
+          <t>1903; 10535</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1063; 5600</t>
+          <t>1087; 5860</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>810; 6933</t>
+          <t>810; 6923</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15408; 31260</t>
+          <t>15347; 30574</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6229; 17937</t>
+          <t>6084; 17986</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2112; 9592</t>
+          <t>2465; 9903</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>23272</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1872; 10427</t>
+          <t>1851; 9998</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5290; 18950</t>
+          <t>5804; 18640</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2408; 11511</t>
+          <t>2365; 11856</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8673; 21724</t>
+          <t>10802; 24193</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4114; 14531</t>
+          <t>4826; 14934</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8447; 22693</t>
+          <t>8540; 22461</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3706; 15104</t>
+          <t>3982; 15896</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3162; 10502</t>
+          <t>3434; 10869</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8201; 21522</t>
+          <t>8446; 22248</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17533; 36505</t>
+          <t>17632; 35521</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8620; 23010</t>
+          <t>9754; 23804</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13215; 29148</t>
+          <t>15133; 31481</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>17663</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3917</t>
+          <t>0; 4287</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2037; 10497</t>
+          <t>1891; 10349</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>766; 5401</t>
+          <t>781; 5484</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6971; 16126</t>
+          <t>6442; 15072</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6151</t>
+          <t>0; 6667</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4953; 15549</t>
+          <t>4986; 15328</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3204; 12871</t>
+          <t>3175; 12634</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3773; 11101</t>
+          <t>3864; 11004</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>887; 7748</t>
+          <t>895; 7026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8019; 20637</t>
+          <t>8853; 21835</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4992; 16057</t>
+          <t>4996; 15722</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12278; 24363</t>
+          <t>12391; 23355</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>22217</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3957</t>
+          <t>0; 3893</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1808; 9506</t>
+          <t>1811; 9045</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3954; 13799</t>
+          <t>4014; 14144</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3820; 13587</t>
+          <t>5550; 17423</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3454; 11798</t>
+          <t>2878; 10656</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3219; 14062</t>
+          <t>3319; 13510</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5551; 17809</t>
+          <t>5726; 17652</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5191; 19015</t>
+          <t>6086; 20550</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3565; 12761</t>
+          <t>3610; 12309</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6742; 19164</t>
+          <t>6565; 18751</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12269; 27720</t>
+          <t>11627; 27457</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11479; 27929</t>
+          <t>13875; 32913</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3643</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>781; 6327</t>
+          <t>0; 6264</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2991; 10339</t>
+          <t>3842; 10923</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1903; 7611</t>
+          <t>1779; 7678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>654; 3806</t>
+          <t>679; 4022</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4290</t>
+          <t>0; 4269</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2084; 10956</t>
+          <t>2079; 11667</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>963; 7487</t>
+          <t>924; 7499</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>335; 2782</t>
+          <t>376; 3007</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>905; 8615</t>
+          <t>935; 9496</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7928; 18578</t>
+          <t>7835; 19421</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4437; 13199</t>
+          <t>4644; 13115</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1600; 6057</t>
+          <t>1628; 6382</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9416</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>869; 6550</t>
+          <t>930; 7367</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1135; 9995</t>
+          <t>1383; 9582</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2657; 10813</t>
+          <t>2612; 10891</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3654; 9774</t>
+          <t>3117; 9834</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2126; 11125</t>
+          <t>2674; 11163</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1037; 9605</t>
+          <t>1074; 9352</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3931; 13878</t>
+          <t>3593; 14055</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1042; 6459</t>
+          <t>1224; 6870</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4882; 15875</t>
+          <t>4960; 15561</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4277; 16950</t>
+          <t>4236; 16315</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8259; 21812</t>
+          <t>8893; 21819</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5838; 13683</t>
+          <t>5695; 14396</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>24154</t>
+          <t>30666</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7456; 18525</t>
+          <t>6885; 18239</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4724; 15620</t>
+          <t>5073; 16272</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4215; 15430</t>
+          <t>3587; 14704</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5046; 14900</t>
+          <t>5627; 17709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10413; 23087</t>
+          <t>10015; 23052</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9299; 23093</t>
+          <t>8514; 23513</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6790; 19176</t>
+          <t>6416; 19340</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>10719; 20605</t>
+          <t>13767; 27287</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20912; 37909</t>
+          <t>20932; 38949</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17410; 33666</t>
+          <t>16420; 34030</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13535; 29514</t>
+          <t>13129; 29452</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>17571; 31651</t>
+          <t>22588; 40097</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>13477</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2769; 11560</t>
+          <t>3115; 11574</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2018; 11731</t>
+          <t>2314; 12123</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6472; 18035</t>
+          <t>6193; 17557</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3876; 11707</t>
+          <t>4896; 13470</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4847; 16227</t>
+          <t>4780; 15581</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9102; 23642</t>
+          <t>9017; 24429</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4545; 15996</t>
+          <t>4517; 15941</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1768; 8050</t>
+          <t>1975; 8770</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>10776; 24244</t>
+          <t>9938; 23513</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13694; 31286</t>
+          <t>14121; 31048</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13231; 30969</t>
+          <t>13624; 29565</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7871; 18804</t>
+          <t>8806; 19934</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>62276</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>26122; 45854</t>
+          <t>26457; 45426</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>49306; 78396</t>
+          <t>48660; 77457</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41819; 67203</t>
+          <t>43294; 68491</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50441; 74818</t>
+          <t>54867; 81090</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>36755; 62079</t>
+          <t>38624; 63528</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>66734; 98841</t>
+          <t>67275; 99595</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>50800; 81415</t>
+          <t>52809; 81571</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>40092; 61718</t>
+          <t>45331; 71653</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>71546; 102438</t>
+          <t>70362; 102503</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>122540; 167472</t>
+          <t>125932; 166310</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>102423; 142450</t>
+          <t>101805; 140282</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>96172; 129947</t>
+          <t>108858; 144554</t>
         </is>
       </c>
     </row>
